--- a/Introtext.xlsx
+++ b/Introtext.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucas/Documents/Experiments/Mood2/github_Mood2/PsychoPy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucas/Documents/Experiments/Mood4/github_Mood4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{279D171D-58A0-164C-8139-10E66DB1F18C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFC8F1DB-155A-B940-8E2D-3C975FE923DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1160" yWindow="760" windowWidth="37220" windowHeight="22840" xr2:uid="{402AE53E-8E8E-A647-AB36-D93CAEC0D9A2}"/>
+    <workbookView xWindow="1160" yWindow="760" windowWidth="16780" windowHeight="22840" xr2:uid="{402AE53E-8E8E-A647-AB36-D93CAEC0D9A2}"/>
   </bookViews>
   <sheets>
     <sheet name="Introtext" sheetId="1" r:id="rId1"/>
@@ -26,19 +26,18 @@
   </si>
   <si>
     <t>Welcome to the reward and subjective well-being task!
-In this experiment, you will have the opportunity to earn money by playing a gambling task. You will also be asked to rate your happiness at various points as you progress through the task.</t>
+In this experiment, you will have the opportunity to earn money by playing a decision-making task. You will also be asked to rate your happiness at various points as you progress through the task.</t>
   </si>
   <si>
-    <t>In the next few steps, we will guide you through the task and how it works, you will then do a minimum of 10 practice trials, and finally you will start the task.</t>
+    <t>In the next few steps, we will guide you through the task and how it works, you will then do a minimum of 10 practice trials, and finally, you will start the task.</t>
   </si>
   <si>
-    <t>The gamble outcome rewards are BIG or MEDIUM, although a proportion of the gambles will have a SMALL reward with a certain (100%) probability.
-You will begin the task with $5. The outcome of the choices you make from then on will count for ADDITIONAL money.
-Please select your gamble choice by pressing the LEFT or RIGHT arrow keys. Once you’ve made your choice the outcome will be applied to your total. 
+    <t>You will begin the task with $5. The outcome of the choices you make from then on will count for ADDITIONAL money.
+Please select your gamble choice by pressing the LEFT or RIGHT arrow keys. Once you’ve made your choice, the outcome will be applied to your total. 
 On the next screen, you will do a few introductory trials.</t>
   </si>
   <si>
-    <t xml:space="preserve">On each trial, you will have the opportunity to earn money. You will be presented with two options, both options will be gambles. Each gamble probability will be indicated by the proportion of the pie that is colored green, each gamble reward size will be indicated by the size of the pie. The probabilities will also be displayed as text. Each gamble has two possible outcomes: either you win and gain the indicated reward, either you lose and earn $0. </t>
+    <t xml:space="preserve">On each trial, you will have the opportunity to earn money. You will be presented with two options: one option will be a certain reward, the other, a gamble. The gamble probability will be indicated by the percentage number. The gamble has two possible outcomes: either you win and gain the indicated reward, either you lose and earn $0. </t>
   </si>
 </sst>
 </file>

--- a/Introtext.xlsx
+++ b/Introtext.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucas/Documents/Experiments/Mood4/github_Mood4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFC8F1DB-155A-B940-8E2D-3C975FE923DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9DECC53-55B9-C34B-BD7E-8676EF668574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1160" yWindow="760" windowWidth="16780" windowHeight="22840" xr2:uid="{402AE53E-8E8E-A647-AB36-D93CAEC0D9A2}"/>
+    <workbookView xWindow="2980" yWindow="600" windowWidth="41600" windowHeight="22840" xr2:uid="{402AE53E-8E8E-A647-AB36-D93CAEC0D9A2}"/>
   </bookViews>
   <sheets>
     <sheet name="Introtext" sheetId="1" r:id="rId1"/>
@@ -32,12 +32,12 @@
     <t>In the next few steps, we will guide you through the task and how it works, you will then do a minimum of 10 practice trials, and finally, you will start the task.</t>
   </si>
   <si>
-    <t>You will begin the task with $5. The outcome of the choices you make from then on will count for ADDITIONAL money.
-Please select your gamble choice by pressing the LEFT or RIGHT arrow keys. Once you’ve made your choice, the outcome will be applied to your total. 
-On the next screen, you will do a few introductory trials.</t>
+    <t>On each trial, you will have the opportunity to earn money. You will be presented with two options: one option will be a certain reward, the other, a gamble. The gamble probability will be indicated by the percentage number. The gamble has two possible outcomes: either you win and gain the indicated reward, either you lose and earn $0. On some trials, you will only be presented with one option, you will have to selected it.</t>
   </si>
   <si>
-    <t xml:space="preserve">On each trial, you will have the opportunity to earn money. You will be presented with two options: one option will be a certain reward, the other, a gamble. The gamble probability will be indicated by the percentage number. The gamble has two possible outcomes: either you win and gain the indicated reward, either you lose and earn $0. </t>
+    <t>You will begin the task with $5. The outcome of the choices you make from then on will count for ADDITIONAL money.
+Please select your option by pressing the LEFT or RIGHT arrow keys, or either, if you are shown only one option. Once you’ve made your choice, the outcome will be applied to your total. 
+On the next screen, you will do a few introductory trials.</t>
   </si>
 </sst>
 </file>
@@ -934,12 +934,12 @@
     </row>
     <row r="4" spans="1:1" ht="192" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="207" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
